--- a/data/editorial_en.xlsx
+++ b/data/editorial_en.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="64">
   <si>
     <t xml:space="preserve">what</t>
   </si>
@@ -37,6 +37,27 @@
     <t xml:space="preserve">why</t>
   </si>
   <si>
+    <t xml:space="preserve">Associate Editor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Since 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\href{https://evohuman.org}{Evolutionary Dynamics of Human Behavior (EDHB)}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Editorial team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selecting appropriate reviewers and managing the review process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contributing to Editorial Board development, focusing on the representation and diversity of the Global South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\href{https://evohuman.org/edhb/editorial-board}{Editorial Board}</t>
+  </si>
+  <si>
     <t xml:space="preserve">Data Editor</t>
   </si>
   <si>
@@ -44,9 +65,6 @@
   </si>
   <si>
     <t xml:space="preserve">\href{https://royalsocietypublishing.org/journal/rspb}{Proceedings of the Royal Society B}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Editorial team</t>
   </si>
   <si>
     <t xml:space="preserve">Ensuring compliance with data and code sharing standards prior to acceptance</t>
@@ -278,7 +296,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -292,10 +310,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -492,8 +506,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
-  <sheetFormatPr defaultColWidth="11.4296875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E1048576"/>
+  <sheetFormatPr defaultColWidth="11.43359375" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.71"/>
@@ -502,7 +516,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="93.63"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -519,348 +533,362 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="s">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2" t="s">
+    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="2" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E9" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2" t="s">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+    <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E11" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="2" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2" t="s">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E14" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2" t="s">
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
+      <c r="C15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="E15" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
-      <c r="E16" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E16" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
+      <c r="B18" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E19" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
-      <c r="B22" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
       <c r="B25" s="2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="2" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
+      <c r="B31" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
+      <c r="E32" s="2" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
+      <c r="A33" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
+      <c r="E34" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
@@ -869,10 +897,33 @@
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
     </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E8" r:id="rId1" display="https://royalsocietypublishing.org/toc/rstb/2022/377/1841"/>
-    <hyperlink ref="E16" r:id="rId2" display="\href{https://nyaspubs.onlinelibrary.wiley.com/journal/17496632}{Annals of the New York Academy of Sciences}"/>
+    <hyperlink ref="E4" r:id="rId1" display="https://evohuman.org/edhb/editorial-board"/>
+    <hyperlink ref="E11" r:id="rId2" display="Theme Issue \textbf{\textit{Voice modulation: from origin and mechanism to social impact}} (\href{https://royalsocietypublishing.org/toc/rstb/2021/376/1840}{\textbf{Part 1}}, \href{https://royalsocietypublishing.org/toc/rstb/2022/377/1841}{\textbf{Part 2}})"/>
+    <hyperlink ref="E19" r:id="rId3" display="\href{https://nyaspubs.onlinelibrary.wiley.com/journal/17496632}{Annals of the New York Academy of Sciences}"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
